--- a/output/laminas_provinciales/prov_i_ingr_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2022_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:06</t>
+    <t xml:space="preserve">2026-09-09 22:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2022_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:02</t>
+    <t xml:space="preserve">2026-09-17 13:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1099,18 +1099,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1070166.12</v>
+        <v>1024937.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>987235.12</v>
+        <v>1070166.12</v>
       </c>
     </row>
     <row r="4">
@@ -1147,10 +1147,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1024937.75</v>
+        <v>987235.12</v>
       </c>
     </row>
   </sheetData>
@@ -1183,101 +1183,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1069051.75</v>
+        <v>1024937.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1191589.88</v>
+        <v>1155245</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1262107.5</v>
+        <v>1233714.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1070166.12</v>
+        <v>1069051.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1218693.5</v>
+        <v>1191589.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1295152.12</v>
+        <v>1262107.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>987235.12</v>
+        <v>1070166.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1112123.88</v>
+        <v>1218693.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1189921.5</v>
+        <v>1295152.12</v>
       </c>
     </row>
     <row r="11">
@@ -1414,35 +1414,35 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1024937.75</v>
+        <v>987235.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1155245</v>
+        <v>1112123.88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>1233714.5</v>
+        <v>1189921.5</v>
       </c>
     </row>
     <row r="26">

--- a/output/laminas_provinciales/prov_i_ingr_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2022_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:34</t>
+    <t xml:space="preserve">2026-09-25 21:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -766,7 +766,7 @@
         <v>938992.62</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>137910.76</v>
+        <v>137910.75</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>14.69</v>

--- a/output/laminas_provinciales/prov_i_ingr_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2022_valparaiso.xlsx
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:33</t>
+    <t xml:space="preserve">2026-10-05 07:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -778,7 +778,7 @@
         <v>859677</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1088366</v>
+        <v>1088367</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>-21</v>
@@ -817,7 +817,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>781806</v>
+        <v>781807</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>957975</v>
